--- a/files/week-07-risk-studio.xlsx
+++ b/files/week-07-risk-studio.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scales" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERT" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Matrix" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reserve and buffer" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Reconciliation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -85,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,55 +106,11 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,14 +144,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1712,446 +1661,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PERT · revised three-point estimates (workdays)</t>
+          <t>Reserve and buffer · LO 7-7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>These estimates replace the ones in the notes. Enter your own formulas in the yellow cells.</t>
+          <t>The reserve total comes from the Register. Fill the yellow cells; the budget lines calculate.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Predecessors</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>t_e</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Baseline budget (from the notes)</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>70000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Event brief</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Contingency reserve (total of the Register's Reserve column)</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>Register!Q13</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Project budget (baseline + contingency reserve)</t>
+        </is>
+      </c>
+      <c r="B6" s="15">
+        <f>B4+B5</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Program draft</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Registration</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Reserve as a share of baseline</t>
+        </is>
+      </c>
+      <c r="B7" s="16">
+        <f>IF(B4&gt;0,B5/B4,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Speakers</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Exhibitors</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Publish program</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>D, E</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>F, G</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Who controls it, and what it pays for</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Contingency reserve</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Management reserve</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Rehearsal</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>One time buffer in the Week 6 conference network</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Activity (ID and name)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Placement rule</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Paths</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Sum t_e</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Sum variance</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>σ</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Z at T_S</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>P(finish ≤ T_S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A–B–D–G–H–I</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="19" t="n"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Days held</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Reason (one or two sentences)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A–C–E–G–H–I</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="19" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A–C–F–H–I</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="19" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Scheduled time T_S (sponsor's date)</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Z for 90% confidence</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1.2816</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>T_E + 1.28σ on the critical path</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Tip: =NORM.S.DIST(Z, TRUE) returns the probability for a Z value.</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>If the reserve is more than a quarter of the baseline, say which rows drive it and whether that is judgement or padding.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:C19"/>
-  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"After an activity with severe risk,At a merge activity,On a noncritical path with little slack,Before an activity that needs a scarce resource"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Whole days, 0 to 30." type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2214,7 +1866,7 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="21" t="n">
+      <c r="A5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -2223,7 +1875,7 @@
       <c r="E5" s="5" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -2232,7 +1884,7 @@
       <c r="E6" s="5" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="17" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -2241,7 +1893,7 @@
       <c r="E7" s="5" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -2250,7 +1902,7 @@
       <c r="E8" s="5" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n"/>
@@ -2259,7 +1911,7 @@
       <c r="E9" s="5" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -2268,7 +1920,7 @@
       <c r="E10" s="5" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="17" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -2277,7 +1929,7 @@
       <c r="E11" s="5" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="21" t="n">
+      <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -2286,7 +1938,7 @@
       <c r="E12" s="5" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -2295,7 +1947,7 @@
       <c r="E13" s="5" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="17" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="5" t="n"/>
